--- a/evaluations/test_reports/throughput/Elapsed_Time/100_Client/direct_client/extracted_stats.xlsx
+++ b/evaluations/test_reports/throughput/Elapsed_Time/100_Client/direct_client/extracted_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,547 +452,197 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1681823183</v>
+        <v>1681823213</v>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>152</v>
+        <v>174.7</v>
       </c>
       <c r="D2" t="n">
-        <v>366.2568976507802</v>
+        <v>327.6007864439204</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1681823184</v>
+        <v>1681823215</v>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>158.2</v>
+        <v>170.4</v>
       </c>
       <c r="D3" t="n">
-        <v>360.6878679968105</v>
+        <v>328.7071190043255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1681823185</v>
+        <v>1681823216</v>
       </c>
       <c r="B4" t="n">
         <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>161</v>
+        <v>169.5</v>
       </c>
       <c r="D4" t="n">
-        <v>356.0726577302684</v>
+        <v>329.7063941675036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1681823187</v>
+        <v>1681823218</v>
       </c>
       <c r="B5" t="n">
         <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>159.1</v>
+        <v>168.5</v>
       </c>
       <c r="D5" t="n">
-        <v>344.4136080830049</v>
+        <v>330.2128984921492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1681823188</v>
+        <v>1681823219</v>
       </c>
       <c r="B6" t="n">
         <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>163.8</v>
+        <v>162.7</v>
       </c>
       <c r="D6" t="n">
-        <v>343.3343399402707</v>
+        <v>329.5406618696233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1681823189</v>
+        <v>1681823220</v>
       </c>
       <c r="B7" t="n">
         <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>165</v>
+        <v>158.7</v>
       </c>
       <c r="D7" t="n">
-        <v>338.7926323921614</v>
+        <v>329.5602174854795</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1681823190</v>
+        <v>1681823221</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>163.4</v>
+        <v>158.6</v>
       </c>
       <c r="D8" t="n">
-        <v>338.4534702953366</v>
+        <v>329.4245372511463</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1681823192</v>
+        <v>1681823222</v>
       </c>
       <c r="B9" t="n">
         <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="D9" t="n">
-        <v>336.7708047700597</v>
+        <v>329.0318167673185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1681823193</v>
+        <v>1681823224</v>
       </c>
       <c r="B10" t="n">
         <v>100</v>
       </c>
       <c r="C10" t="n">
-        <v>167.7</v>
+        <v>156.2</v>
       </c>
       <c r="D10" t="n">
-        <v>337.4644381450182</v>
+        <v>327.3858711204648</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1681823194</v>
+        <v>1681823225</v>
       </c>
       <c r="B11" t="n">
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>167.1</v>
+        <v>151.8</v>
       </c>
       <c r="D11" t="n">
-        <v>337.0990848415112</v>
+        <v>327.9227976165066</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1681823195</v>
+        <v>1681823227</v>
       </c>
       <c r="B12" t="n">
         <v>100</v>
       </c>
       <c r="C12" t="n">
-        <v>170.8</v>
+        <v>159.2</v>
       </c>
       <c r="D12" t="n">
-        <v>336.5505189977141</v>
+        <v>329.6275073824522</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1681823197</v>
+        <v>1681823228</v>
       </c>
       <c r="B13" t="n">
         <v>100</v>
       </c>
       <c r="C13" t="n">
-        <v>171.6</v>
+        <v>158.9</v>
       </c>
       <c r="D13" t="n">
-        <v>336.5674953341884</v>
+        <v>328.4249419011426</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1681823198</v>
+        <v>1681823229</v>
       </c>
       <c r="B14" t="n">
         <v>100</v>
       </c>
       <c r="C14" t="n">
-        <v>166.7</v>
+        <v>160.2</v>
       </c>
       <c r="D14" t="n">
-        <v>337.8995045371677</v>
+        <v>328.8889984639999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1681823199</v>
+        <v>1681823230</v>
       </c>
       <c r="B15" t="n">
         <v>100</v>
       </c>
       <c r="C15" t="n">
-        <v>157.8</v>
+        <v>161.6</v>
       </c>
       <c r="D15" t="n">
-        <v>337.8767444133654</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1681823201</v>
-      </c>
-      <c r="B16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C16" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>337.9609146406428</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1681823202</v>
-      </c>
-      <c r="B17" t="n">
-        <v>100</v>
-      </c>
-      <c r="C17" t="n">
-        <v>157.6</v>
-      </c>
-      <c r="D17" t="n">
-        <v>336.8351222669888</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1681823203</v>
-      </c>
-      <c r="B18" t="n">
-        <v>100</v>
-      </c>
-      <c r="C18" t="n">
-        <v>150.9</v>
-      </c>
-      <c r="D18" t="n">
-        <v>335.9018609709872</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1681823204</v>
-      </c>
-      <c r="B19" t="n">
-        <v>100</v>
-      </c>
-      <c r="C19" t="n">
-        <v>157.8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>334.9505506596266</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1681823205</v>
-      </c>
-      <c r="B20" t="n">
-        <v>100</v>
-      </c>
-      <c r="C20" t="n">
-        <v>154.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>335.0143089874394</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1681823206</v>
-      </c>
-      <c r="B21" t="n">
-        <v>100</v>
-      </c>
-      <c r="C21" t="n">
-        <v>154.2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>333.4529375843542</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1681823208</v>
-      </c>
-      <c r="B22" t="n">
-        <v>100</v>
-      </c>
-      <c r="C22" t="n">
-        <v>156.8</v>
-      </c>
-      <c r="D22" t="n">
-        <v>331.828006370219</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1681823209</v>
-      </c>
-      <c r="B23" t="n">
-        <v>100</v>
-      </c>
-      <c r="C23" t="n">
-        <v>155</v>
-      </c>
-      <c r="D23" t="n">
-        <v>329.8397409069273</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1681823210</v>
-      </c>
-      <c r="B24" t="n">
-        <v>100</v>
-      </c>
-      <c r="C24" t="n">
-        <v>162</v>
-      </c>
-      <c r="D24" t="n">
-        <v>329.2152525740071</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1681823211</v>
-      </c>
-      <c r="B25" t="n">
-        <v>100</v>
-      </c>
-      <c r="C25" t="n">
-        <v>168.4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>328.3261817763791</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1681823212</v>
-      </c>
-      <c r="B26" t="n">
-        <v>100</v>
-      </c>
-      <c r="C26" t="n">
-        <v>173.7</v>
-      </c>
-      <c r="D26" t="n">
-        <v>328.6788087607101</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1681823213</v>
-      </c>
-      <c r="B27" t="n">
-        <v>100</v>
-      </c>
-      <c r="C27" t="n">
-        <v>174.7</v>
-      </c>
-      <c r="D27" t="n">
-        <v>327.6007864439204</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1681823215</v>
-      </c>
-      <c r="B28" t="n">
-        <v>100</v>
-      </c>
-      <c r="C28" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="D28" t="n">
-        <v>328.7071190043255</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1681823216</v>
-      </c>
-      <c r="B29" t="n">
-        <v>100</v>
-      </c>
-      <c r="C29" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="D29" t="n">
-        <v>329.7063941675036</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1681823218</v>
-      </c>
-      <c r="B30" t="n">
-        <v>100</v>
-      </c>
-      <c r="C30" t="n">
-        <v>168.5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>330.2128984921492</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1681823219</v>
-      </c>
-      <c r="B31" t="n">
-        <v>100</v>
-      </c>
-      <c r="C31" t="n">
-        <v>162.7</v>
-      </c>
-      <c r="D31" t="n">
-        <v>329.5406618696233</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1681823220</v>
-      </c>
-      <c r="B32" t="n">
-        <v>100</v>
-      </c>
-      <c r="C32" t="n">
-        <v>158.7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>329.5602174854795</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1681823221</v>
-      </c>
-      <c r="B33" t="n">
-        <v>100</v>
-      </c>
-      <c r="C33" t="n">
-        <v>158.6</v>
-      </c>
-      <c r="D33" t="n">
-        <v>329.4245372511463</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1681823222</v>
-      </c>
-      <c r="B34" t="n">
-        <v>100</v>
-      </c>
-      <c r="C34" t="n">
-        <v>152</v>
-      </c>
-      <c r="D34" t="n">
-        <v>329.0318167673185</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1681823224</v>
-      </c>
-      <c r="B35" t="n">
-        <v>100</v>
-      </c>
-      <c r="C35" t="n">
-        <v>156.2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>327.3858711204648</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>1681823225</v>
-      </c>
-      <c r="B36" t="n">
-        <v>100</v>
-      </c>
-      <c r="C36" t="n">
-        <v>151.8</v>
-      </c>
-      <c r="D36" t="n">
-        <v>327.9227976165066</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1681823227</v>
-      </c>
-      <c r="B37" t="n">
-        <v>100</v>
-      </c>
-      <c r="C37" t="n">
-        <v>159.2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>329.6275073824522</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1681823228</v>
-      </c>
-      <c r="B38" t="n">
-        <v>100</v>
-      </c>
-      <c r="C38" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="D38" t="n">
-        <v>328.4249419011426</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1681823229</v>
-      </c>
-      <c r="B39" t="n">
-        <v>100</v>
-      </c>
-      <c r="C39" t="n">
-        <v>160.2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>328.8889984639999</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1681823230</v>
-      </c>
-      <c r="B40" t="n">
-        <v>100</v>
-      </c>
-      <c r="C40" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="D40" t="n">
         <v>328.2692937403716</v>
       </c>
     </row>
